--- a/src/Tests/Samples.VerifyExcelStream.verified.xlsx
+++ b/src/Tests/Samples.VerifyExcelStream.verified.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="10320" yWindow="3396" windowWidth="30960" windowHeight="12120" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="DeterministicId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029"/>
